--- a/文档/文明和领袖（模组）.xlsx
+++ b/文档/文明和领袖（模组）.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Admin\Documents\GitHub\Sistine_civ6mod\文档\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="19200" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="93">
   <si>
     <r>
       <rPr>
@@ -841,13 +846,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>纯白天启</t>
     </r>
     <r>
@@ -858,18 +856,112 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-创立万神殿解锁“神秘主义”市政并提供每回合+2大预言家点数。与山脉、森林或自然奇观相邻的迷人或惊艳单元格+1信仰值。森林单元格为相邻的单元格提供额外+1魅力。解锁“王权神授”市政后获得特色单位“爱梅斯巫女”。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>创立万神殿解锁“神秘主义”市政并提供每回合+2大预言家点数。与山脉、森林或自然奇观相邻的迷人或惊艳单元格+1信仰值。森林单元格为相邻的单元格提供额外+1魅力。解锁“</t>
+创立万神殿</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>解锁“神秘主义”市政并</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>提供每回合+2大预言家点数。与山脉、森林或自然奇观相邻的迷人或惊艳单元格+1信仰值。</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>森林单元格为相邻的单元格提供额外+1魅力。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>拥有圣地的城市，所有单元格+1魅力。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>解锁“王权神授”市政后获得特色单位“爱梅斯巫女”。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>创立万神殿</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>解锁“神秘主义”市政并</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>提供每回合+2大预言家点数。与山脉、森林或自然奇观相邻的迷人或惊艳单元格+1信仰值。</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>森林单元格为相邻的单元格提供额外+1魅力。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>拥有圣地的城市，所有单元格+1魅力。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>解锁“</t>
     </r>
     <r>
       <rPr>
@@ -899,14 +991,27 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>极光圣域</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>未改良的迷人或惊艳魅力的平原、草原和冻土单元格的基础地形产出增加至2食物和2生产力。若城市有国家公园，以上效果额外+1食物、+1生产力。</t>
     </r>
     <r>
       <rPr>
@@ -917,7 +1022,27 @@
       </rPr>
       <t xml:space="preserve">
 【无越南包】古罗马剧场、灯塔、神社、大学、银行和工厂为所在城市所有迷人的未改良单元格+1相应产出，惊艳的未改良单元格则+2。单位位于迷人或惊艳单元格每回合可多恢复10点生命值。
-【越南包】保护区从相邻冻土单元格获得+1食物，获得与其住房加成相等的文化值与生产力。保护区建筑的效果范围增大1且可以使用信仰值购买。单位位于迷人或惊艳单元格每回合可多恢复10点生命值。</t>
+【越南包】</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>保护区从相邻冻土单元格获得+1食物，获得与其住房加成相等的文化值与生产力。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>保护区建筑的效果范围增大1且可以使用信仰值购买。单位位于迷人或惊艳单元格每回合可多恢复10点生命值。</t>
     </r>
   </si>
   <si>
@@ -1138,29 +1263,47 @@
 拥有学院区域的城市科技值+10%、生产力+5%。若一座城市的3个单元格范围内有5个海岸单元格，且这些单元格为您所拥有，则这些产出加倍。</t>
   </si>
   <si>
+    <r>
+      <t>拥有学院区域的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>城市科技值、生产力+5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。若一座城市的3个单元格范围内有5个海岸单元格，且这些单元格为您所拥有，则这些产出加倍。</t>
+    </r>
+  </si>
+  <si>
     <t>宇宙蓝闪光
 【迭起兴衰】学院从海岸单元格获得标准相邻加成，河流获得大量相邻加成。陆地远程单位在与水域相邻的单元格+1射程。解锁“写作”科技后与水域相邻的单元格+1生产力。建成宇航中心区域后，即可解锁“纳米技术”科技。
 【风云变幻】学院从海岸单元格获得标准相邻加成，河流获得大量相邻加成。陆地远程单位在与水域相邻的单元格+1射程。解锁“写作”科技后与水域相邻的单元格+1生产力。完成“启动火星殖民”项目后，即可解锁“外星任务”科技。</t>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>【风云变幻】学院从海岸单元格获得标准相邻加成，河流获得大量相邻加成。陆地远程单位在与水域相邻的单元格+1射程。解锁“</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>书写</t>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>学徒制度</t>
     </r>
     <r>
       <rPr>
@@ -1221,9 +1364,6 @@
     </r>
   </si>
   <si>
-    <t>相邻或位于海岸或湖泊的改良设施获得1点产出，在科技值、生产力或文化值之中随机选择。</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1243,6 +1383,31 @@
       </rPr>
       <t xml:space="preserve">
 每个相邻或位于海岸或湖泊的建筑和改良设施为所在城市 +3% 科技值、生产力和文化值，每个相邻或位于海岸或湖泊的区域则 +9%，每座城市上限 30%。远程单位的攻击使目标单位在3回合内 -7 战斗力。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>每个相邻或位于海岸或湖泊的建筑和改良设施为所在城市 +3% 科技值、生产力和文化值，</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>每个相邻或位于海岸或湖泊的区域则 +9%，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>每座城市上限 30%。远程单位的攻击使目标单位在3回合内 -7 战斗力。</t>
     </r>
   </si>
 </sst>
@@ -1444,16 +1609,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <strike/>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
+      <color rgb="FFFFC000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <strike/>
       <sz val="11"/>
-      <color rgb="FFFFC000"/>
+      <color rgb="FF00B050"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2750,7 +2915,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" ht="148.5" spans="1:12">
+    <row r="9" ht="202.5" spans="1:12">
       <c r="A9" s="5"/>
       <c r="B9" s="5" t="s">
         <v>66</v>
@@ -2833,7 +2998,9 @@
       <c r="C12" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="5"/>
+      <c r="D12" s="5" t="s">
+        <v>85</v>
+      </c>
       <c r="E12" s="5" t="s">
         <v>10</v>
       </c>
@@ -2841,28 +3008,26 @@
         <v>10</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
       <c r="K12" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" ht="81" spans="1:12">
       <c r="A13" s="5"/>
       <c r="B13" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" s="10" t="s">
         <v>90</v>
       </c>
+      <c r="D13" s="10"/>
       <c r="E13" s="5" t="s">
         <v>10</v>
       </c>
@@ -2872,7 +3037,9 @@
       <c r="G13" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="H13" s="5"/>
+      <c r="H13" s="5" t="s">
+        <v>92</v>
+      </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
